--- a/data/trans_orig/P2A_enfcro_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20460</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34106</t>
+          <t>33792</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>25560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39072</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50196</t>
+          <t>49455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69090</t>
+          <t>69534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44453</t>
+          <t>44767</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58099</t>
+          <t>57829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>48707</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63094</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97933</t>
+          <t>97489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116827</t>
+          <t>117568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55716</t>
+          <t>56522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77526</t>
+          <t>76865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60248</t>
+          <t>59516</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80388</t>
+          <t>81170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120397</t>
+          <t>120873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151311</t>
+          <t>151464</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109720</t>
+          <t>110381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131530</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108343</t>
+          <t>107561</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>128483</t>
+          <t>129215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>224666</t>
+          <t>224513</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255580</t>
+          <t>255104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34155</t>
+          <t>34863</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49076</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42486</t>
+          <t>42725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59457</t>
+          <t>59483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>81423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103937</t>
+          <t>104281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37403</t>
+          <t>36701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52324</t>
+          <t>51616</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43804</t>
+          <t>43778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60775</t>
+          <t>60536</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85803</t>
+          <t>85459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108726</t>
+          <t>108317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54927</t>
+          <t>55564</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>74746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63510</t>
+          <t>63791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82819</t>
+          <t>83681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123946</t>
+          <t>124646</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151196</t>
+          <t>151721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>76329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96148</t>
+          <t>95511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65275</t>
+          <t>64413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84584</t>
+          <t>84303</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147973</t>
+          <t>147448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175223</t>
+          <t>174523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182877</t>
+          <t>181145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>216941</t>
+          <t>217000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208567</t>
+          <t>208778</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243856</t>
+          <t>245146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>401501</t>
+          <t>399580</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>451997</t>
+          <t>453282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>286418</t>
+          <t>286359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320482</t>
+          <t>322214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>284693</t>
+          <t>283403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319982</t>
+          <t>319771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>579911</t>
+          <t>578626</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>630407</t>
+          <t>632328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33287</t>
+          <t>32367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48661</t>
+          <t>48609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38926</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56765</t>
+          <t>56341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75867</t>
+          <t>76282</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100224</t>
+          <t>100423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55460</t>
+          <t>55512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70834</t>
+          <t>71754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55278</t>
+          <t>55702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73117</t>
+          <t>73833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115939</t>
+          <t>115740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140296</t>
+          <t>139881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62712</t>
+          <t>64008</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83215</t>
+          <t>83874</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73687</t>
+          <t>73039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97323</t>
+          <t>96818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143229</t>
+          <t>143308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175983</t>
+          <t>174878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76129</t>
+          <t>75470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96632</t>
+          <t>95336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95901</t>
+          <t>96406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119537</t>
+          <t>120185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176585</t>
+          <t>177690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209339</t>
+          <t>209260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>41921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59095</t>
+          <t>57599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>41774</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57660</t>
+          <t>58777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89148</t>
+          <t>89459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112632</t>
+          <t>112211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38885</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55590</t>
+          <t>56059</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44152</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59720</t>
+          <t>60038</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87161</t>
+          <t>87582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110645</t>
+          <t>110334</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,22%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49025</t>
+          <t>48055</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>65830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66590</t>
+          <t>66967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85822</t>
+          <t>84861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120768</t>
+          <t>120368</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146438</t>
+          <t>145181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48904</t>
+          <t>49690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66495</t>
+          <t>67465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45880</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65112</t>
+          <t>64735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100783</t>
+          <t>102040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126453</t>
+          <t>126853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205564</t>
+          <t>204644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239769</t>
+          <t>239956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>239227</t>
+          <t>240217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>276099</t>
+          <t>278303</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>454290</t>
+          <t>454476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>509320</t>
+          <t>506927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>237196</t>
+          <t>237009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>271401</t>
+          <t>272321</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>262682</t>
+          <t>260478</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>299554</t>
+          <t>298564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>506426</t>
+          <t>508819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>561456</t>
+          <t>561270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25034</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39343</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28787</t>
+          <t>29320</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43608</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58103</t>
+          <t>58384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79580</t>
+          <t>79309</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63361</t>
+          <t>62835</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77670</t>
+          <t>78113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54659</t>
+          <t>53485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69480</t>
+          <t>68947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121391</t>
+          <t>121662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142868</t>
+          <t>142587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51564</t>
+          <t>51112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70441</t>
+          <t>70212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63239</t>
+          <t>63536</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85703</t>
+          <t>86339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120819</t>
+          <t>121090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150358</t>
+          <t>150252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85824</t>
+          <t>86053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104701</t>
+          <t>105153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124889</t>
+          <t>124253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147353</t>
+          <t>147056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>216499</t>
+          <t>216605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>246038</t>
+          <t>245767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>53710</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73174</t>
+          <t>73690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50254</t>
+          <t>51228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69798</t>
+          <t>69674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110502</t>
+          <t>109868</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>138086</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71140</t>
+          <t>70624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90439</t>
+          <t>90604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62373</t>
+          <t>62497</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81917</t>
+          <t>80943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>138125</t>
+          <t>138399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165983</t>
+          <t>166617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56587</t>
+          <t>55622</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75464</t>
+          <t>75103</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53317</t>
+          <t>52626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73825</t>
+          <t>72467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116601</t>
+          <t>116470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143243</t>
+          <t>143823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,05%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46642</t>
+          <t>47003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65519</t>
+          <t>66484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56179</t>
+          <t>57537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76687</t>
+          <t>77378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108867</t>
+          <t>108287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135509</t>
+          <t>135640</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205187</t>
+          <t>206228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>245939</t>
+          <t>241106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>216460</t>
+          <t>214222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>254440</t>
+          <t>253416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>429534</t>
+          <t>430455</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>483422</t>
+          <t>483498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>279451</t>
+          <t>284284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320203</t>
+          <t>319162</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>316593</t>
+          <t>317617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>354573</t>
+          <t>356811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>613001</t>
+          <t>612925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>666889</t>
+          <t>665968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48560</t>
+          <t>48458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55320</t>
+          <t>54979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57596</t>
+          <t>57504</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61056</t>
+          <t>61057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108535</t>
+          <t>108649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115927</t>
+          <t>115609</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>387</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148121</t>
+          <t>146844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155965</t>
+          <t>155585</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163054</t>
+          <t>163162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174825</t>
+          <t>175105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>313904</t>
+          <t>313909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>328347</t>
+          <t>328781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13072</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>27944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>157745</t>
+          <t>157527</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168305</t>
+          <t>168822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193402</t>
+          <t>195022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207189</t>
+          <t>207355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357546</t>
+          <t>355847</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373301</t>
+          <t>372428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>17468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28832</t>
+          <t>30531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>257058</t>
+          <t>257500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>269280</t>
+          <t>269107</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>281585</t>
+          <t>280502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>296381</t>
+          <t>296646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>543189</t>
+          <t>543732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>563111</t>
+          <t>562972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>24981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>37208</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>623857</t>
+          <t>624388</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>643158</t>
+          <t>642736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>708305</t>
+          <t>709120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>732249</t>
+          <t>732502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1339500</t>
+          <t>1340125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1368932</t>
+          <t>1370764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22997</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42298</t>
+          <t>41767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29723</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>57363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88627</t>
+          <t>88002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_enfcro_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32410</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24900</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39906</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>27312</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20730</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33792</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20769</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>34051</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>34,77%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>32410</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>25560</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>39757</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>36,64%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49455</t>
+          <t>49246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69534</t>
+          <t>69459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56054</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48558</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63564</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>63,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>54,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>71,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51247</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44767</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57829</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>44508</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>57790</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>65,23%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56054</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48707</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62904</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>63,36%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97489</t>
+          <t>97564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117568</t>
+          <t>117777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>70104</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>59925</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>81310</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>43,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>66552</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>56522</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>76865</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>56590</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>78108</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>35,54%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>41,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>70104</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>59516</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>81170</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>37,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120873</t>
+          <t>122674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151464</t>
+          <t>152483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>118627</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>107421</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>128806</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>62,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>56,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>120694</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>110381</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>130724</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>109138</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>130656</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>64,46%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>118627</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>107561</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>129215</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>62,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>224513</t>
+          <t>223494</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255104</t>
+          <t>253303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>50803</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42845</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>58573</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>41,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>41679</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34863</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49778</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34080</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>49398</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>48,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>50803</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>42725</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>59483</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,2%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81423</t>
+          <t>82429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104281</t>
+          <t>104612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>52458</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>44688</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>60416</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>58,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>44800</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36701</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51616</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>37081</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>52399</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>51,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,44%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>59,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>52458</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>43778</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>60536</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,8%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85459</t>
+          <t>85128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108317</t>
+          <t>107311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>72916</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>62482</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>81854</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>49,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>42,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>64602</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>55564</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>74746</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>55263</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>75364</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>42,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,78%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>72916</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>63791</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>83681</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124646</t>
+          <t>122940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151721</t>
+          <t>150593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>75178</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66240</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>85612</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>50,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>86473</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>76329</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>95511</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>75711</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>95812</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>57,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>75178</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>64413</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>84303</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>50,76%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147448</t>
+          <t>148576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174523</t>
+          <t>176229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>208384</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>245623</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>39,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>46,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>200145</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>181145</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>217000</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>181684</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>218077</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>39,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>226233</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>208778</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>245146</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>399580</t>
+          <t>400649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453282</t>
+          <t>450187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>302316</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>282926</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>320165</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>57,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>53,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>60,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>450</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>303214</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>286359</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>322214</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>285282</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>321675</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>60,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>56,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>64,01%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>302316</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>283403</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>319771</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>57,2%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>578626</t>
+          <t>581721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>632328</t>
+          <t>631259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47533</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39386</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>56631</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>40839</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32367</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48609</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32282</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48830</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>47533</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>38210</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>56341</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,42%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76282</t>
+          <t>75841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100423</t>
+          <t>99695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64510</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55412</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72657</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>57,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>49,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>64,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>63282</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55512</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>71754</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>55291</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>71839</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>60,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>68,91%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64510</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55702</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73833</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>57,58%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115740</t>
+          <t>116468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139881</t>
+          <t>140322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>85128</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>74344</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>96553</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>44,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>38,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>74003</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>64008</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>83874</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>64104</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>84554</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>46,44%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40,17%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>85128</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>73039</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>96818</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>44,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143308</t>
+          <t>145310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174878</t>
+          <t>174925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108096</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96671</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>118880</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>55,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,03%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>61,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>85341</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>75470</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>95336</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>74790</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>95240</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>53,56%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108096</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>96406</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>120185</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>55,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177690</t>
+          <t>177643</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209260</t>
+          <t>207258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,79%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>50356</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41480</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>58126</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>50258</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>41921</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>57599</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>41859</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>57993</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>50356</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>41774</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58777</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89459</t>
+          <t>89847</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112211</t>
+          <t>111978</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,05%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51456</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43686</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>60332</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>47722</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40381</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>56059</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>39987</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>56121</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>48,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>41,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>57,21%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>51456</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>43035</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>60038</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,54%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87582</t>
+          <t>87815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110334</t>
+          <t>109946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,03%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>76055</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>67306</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>85268</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>57,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>51,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>57295</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>48055</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>65830</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>48537</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>65868</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>49,6%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>41,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>76055</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>66967</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>84861</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>57,75%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120368</t>
+          <t>119844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145181</t>
+          <t>144855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55647</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>46434</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>64396</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>35,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>48,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>58225</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>49690</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>67465</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>49652</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>66983</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>50,4%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>58,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>55647</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>46841</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>64735</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>42,25%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102040</t>
+          <t>102366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126853</t>
+          <t>127377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,52%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>238688</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>276489</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>48,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>44,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>320</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>222394</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>204644</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>239956</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>205485</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>239569</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>46,63%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>259073</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>240217</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>278303</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>48,08%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>454476</t>
+          <t>455074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>506927</t>
+          <t>505661</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>279708</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>262292</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>300093</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>51,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>48,68%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>55,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>254571</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>237009</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>272321</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>237396</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>271480</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>53,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>57,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>279708</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>260478</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>298564</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>51,92%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>508819</t>
+          <t>510085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>561270</t>
+          <t>560672</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36779</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29948</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44815</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,48%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32149</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24591</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39869</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24933</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>39674</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>36779</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29320</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>44782</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,43%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58384</t>
+          <t>58500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79309</t>
+          <t>79450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>61488</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53452</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68319</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>62,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>54,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,52%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70555</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>62835</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>78113</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>63030</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>77771</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>68,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61488</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53485</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68947</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>62,57%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121662</t>
+          <t>121521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142587</t>
+          <t>142471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>74341</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64275</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>85640</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>60715</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>51112</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>70212</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>50837</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>70915</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>38,85%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>74341</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>63536</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86339</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121090</t>
+          <t>121165</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150252</t>
+          <t>150844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>136251</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>124952</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>146317</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>95550</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>86053</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>105153</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>85350</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>105428</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>61,15%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>136251</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>124253</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>147056</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,7%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>216605</t>
+          <t>216013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>245767</t>
+          <t>245692</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60206</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50884</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>69412</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>52,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>63671</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53710</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73690</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>53992</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>73493</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>60206</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>69674</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109868</t>
+          <t>110353</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138086</t>
+          <t>136055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71965</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>62759</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81287</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>54,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>47,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>61,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>80643</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70624</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>90604</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>70821</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>90322</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>55,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>48,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71965</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>62497</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>80943</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>54,45%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>138399</t>
+          <t>140430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166617</t>
+          <t>166132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>63292</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>53751</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>73007</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>48,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>41,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>56,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>66139</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>55622</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>75103</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>56942</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>75934</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>54,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>61,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>63292</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>52626</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>72467</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>48,68%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116470</t>
+          <t>114569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143823</t>
+          <t>141637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>66712</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>56997</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>76253</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>58,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>55967</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47003</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>66484</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>46172</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>65164</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>45,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>38,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>54,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>66712</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>57537</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>77378</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108287</t>
+          <t>110473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135640</t>
+          <t>137541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>216293</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>255101</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>222674</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>206228</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>241106</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>204609</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>239933</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>42,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>234618</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>214222</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>253416</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>430455</t>
+          <t>431014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>483498</t>
+          <t>485340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>336415</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>315932</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>354740</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>55,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>62,12%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>460</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>302716</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>284284</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>319162</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>285457</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>320781</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>57,62%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>54,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>60,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>336415</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>317617</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>356811</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>58,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>612925</t>
+          <t>611083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>665968</t>
+          <t>665409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,69%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49522</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47731</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50244</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>52736</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>48458</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>54979</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>60123</t>
+          <t>48115</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57504</t>
+          <t>44475</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61057</t>
+          <t>50093</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>112858</t>
+          <t>97637</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108649</t>
+          <t>94064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115609</t>
+          <t>99895</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2532</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9053</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>147910</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>142971</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>151860</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>90,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>152658</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>146844</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>155585</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>170180</t>
+          <t>138924</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163162</t>
+          <t>133426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175105</t>
+          <t>142040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>322838</t>
+          <t>286833</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>313909</t>
+          <t>280118</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>328781</t>
+          <t>291871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9612</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5662</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14551</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6641</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3714</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12455</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27944</t>
+          <t>22921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>189826</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>181900</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>194654</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>90,89%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>163938</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>157527</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>168822</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>94,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>201945</t>
+          <t>165411</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>195022</t>
+          <t>158979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207355</t>
+          <t>170038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>365883</t>
+          <t>355237</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>355847</t>
+          <t>345332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>372428</t>
+          <t>363097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10300</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5472</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18226</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9950</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5066</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16361</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17468</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13950</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30531</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>276941</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>267644</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>283465</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>326</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>264336</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>257500</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>269107</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>93,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>289921</t>
+          <t>245029</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>280502</t>
+          <t>237602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>296646</t>
+          <t>249671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>554255</t>
+          <t>521970</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>543732</t>
+          <t>511494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>562972</t>
+          <t>530086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15704</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9180</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25001</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11122</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6351</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17958</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24981</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17968</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37208</t>
+          <t>37704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>664197</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>651951</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>673502</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>93,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>893</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>633667</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>624388</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>642736</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>93,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>722169</t>
+          <t>597478</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>709120</t>
+          <t>586887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>732502</t>
+          <t>605754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1355836</t>
+          <t>1261676</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1340125</t>
+          <t>1246306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1370764</t>
+          <t>1274903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36632</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>27327</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>48878</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>32488</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>23419</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>41767</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39803</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29470</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52852</t>
+          <t>42791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>72291</t>
+          <t>68832</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57363</t>
+          <t>55605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88002</t>
+          <t>84202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
